--- a/data/summer_schedule_2026.xlsx
+++ b/data/summer_schedule_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25-May (Mon)</t>
+          <t>19-May (Tue)</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01-Jun (Mon)</t>
+          <t>21-May (Thu)</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>08-Jun (Mon)</t>
+          <t>26-May (Tue)</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15-Jun (Mon)</t>
+          <t>28-May (Thu)</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22-Jun (Mon)</t>
+          <t>02-Jun (Tue)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29-Jun (Mon)</t>
+          <t>04-Jun (Thu)</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06-Jul (Mon)</t>
+          <t>09-Jun (Tue)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13-Jul (Mon)</t>
+          <t>11-Jun (Thu)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20-Jul (Mon)</t>
+          <t>16-Jun (Tue)</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>27-Jul (Mon)</t>
+          <t>18-Jun (Thu)</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>03-Aug (Mon)</t>
+          <t>23-Jun (Tue)</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10-Aug (Mon)</t>
+          <t>25-Jun (Thu)</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17-Aug (Mon)</t>
+          <t>30-Jun (Tue)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>L14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>02-Jul (Thu)</t>
         </is>
       </c>
     </row>
